--- a/s2422_kk_on_drt.xlsx
+++ b/s2422_kk_on_drt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitra\Downloads\matlab analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125D3EAF-685C-4284-A92C-44A289F7AE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EBA72B-1B01-4513-AF49-E479F81D4D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{1201A2BE-8D73-4181-9E82-4CC0BF61038E}"/>
   </bookViews>
